--- a/survey_templates/035_romance_reading_habits_survey--survey_templates.xlsx
+++ b/survey_templates/035_romance_reading_habits_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'authors'}</t>
+          <t>authors</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'authors'}</t>
+          <t>authors</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'publishers'}</t>
+          <t>publishers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'publishers'}</t>
+          <t>publishers</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'librarians'}</t>
+          <t>librarians</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'librarians'}</t>
+          <t>librarians</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'book_communities'}</t>
+          <t>book_communities</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'book_communities'}</t>
+          <t>book communities</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'romance'}</t>
+          <t>romance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Romance'}</t>
+          <t>Romance</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'fiction'}</t>
+          <t>fiction</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Fiction'}</t>
+          <t>Fiction</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'non-fiction'}</t>
+          <t>non-fiction</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Fiction'}</t>
+          <t>Non-Fiction</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'fantasy'}</t>
+          <t>fantasy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Fantasy'}</t>
+          <t>Fantasy</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'mystery'}</t>
+          <t>mystery</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Mystery'}</t>
+          <t>Mystery</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'thriller'}</t>
+          <t>thriller</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Thriller'}</t>
+          <t>Thriller</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'horror'}</t>
+          <t>horror</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Horror'}</t>
+          <t>Horror</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'science_fiction'}</t>
+          <t>science_fiction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Science Fiction'}</t>
+          <t>Science Fiction</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'hardcover'}</t>
+          <t>hardcover</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Hardcover'}</t>
+          <t>Hardcover</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'paperback'}</t>
+          <t>paperback</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Paperback'}</t>
+          <t>Paperback</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'e-book'}</t>
+          <t>e-book</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'E-Book'}</t>
+          <t>E-Book</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'audiobook'}</t>
+          <t>audiobook</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Audiobook'}</t>
+          <t>Audiobook</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'book_clubs'}</t>
+          <t>book_clubs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Book Clubs'}</t>
+          <t>Book Clubs</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'online_communities'}</t>
+          <t>online_communities</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Online Communities'}</t>
+          <t>Online Communities</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'friends'}</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Friends'}</t>
+          <t>Friends</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'short_story_collection'}</t>
+          <t>short_story_collection</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Short Story Collection'}</t>
+          <t>Short Story Collection</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'100-200_pages'}</t>
+          <t>100-200_pages</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': '100-200 pages'}</t>
+          <t>100-200 pages</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'200-300_pages'}</t>
+          <t>200-300_pages</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': '200-300 pages'}</t>
+          <t>200-300 pages</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'300-400_pages'}</t>
+          <t>300-400_pages</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': '300-400 pages'}</t>
+          <t>300-400 pages</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'400-600_pages'}</t>
+          <t>400-600_pages</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': '400-600 pages'}</t>
+          <t>400-600 pages</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'600-800_pages'}</t>
+          <t>600-800_pages</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': '600-800 pages'}</t>
+          <t>600-800 pages</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'800+_pages'}</t>
+          <t>800+_pages</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': '800+ pages'}</t>
+          <t>800+ pages</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'physical_book'}</t>
+          <t>physical_book</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Physical Book'}</t>
+          <t>Physical Book</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'e-book'}</t>
+          <t>e-book</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'E-Book'}</t>
+          <t>E-Book</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'audiobook'}</t>
+          <t>audiobook</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Audiobook'}</t>
+          <t>Audiobook</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'e-reader'}</t>
+          <t>e-reader</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'E-Reader'}</t>
+          <t>E-Reader</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Tablet'}</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'smartphone'}</t>
+          <t>smartphone</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'Smartphone'}</t>
+          <t>Smartphone</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'paperback'}</t>
+          <t>paperback</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Paperback'}</t>
+          <t>Paperback</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'hardcover'}</t>
+          <t>hardcover</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Hardcover'}</t>
+          <t>Hardcover</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'work'}</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Work'}</t>
+          <t>Work</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'school'}</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'School'}</t>
+          <t>School</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'public_place'}</t>
+          <t>public_place</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'Public Place'}</t>
+          <t>Public Place</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'bookstore'}</t>
+          <t>bookstore</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Bookstore'}</t>
+          <t>Bookstore</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'recommendation'}</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'Recommendation'}</t>
+          <t>Recommendation</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'gift'}</t>
+          <t>gift</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'Gift'}</t>
+          <t>Gift</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'value':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'value': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'value':_'fiction'}</t>
+          <t>fiction</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'value': 'Fiction'}</t>
+          <t>Fiction</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'value':_'non-fiction'}</t>
+          <t>non-fiction</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Fiction'}</t>
+          <t>Non-Fiction</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'value':_'comic_books'}</t>
+          <t>comic_books</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'value': 'Comic Books'}</t>
+          <t>Comic Books</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'value':_'magazine'}</t>
+          <t>magazine</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'value': 'Magazine'}</t>
+          <t>Magazine</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'value':_'bookstore'}</t>
+          <t>bookstore</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'value': 'Bookstore'}</t>
+          <t>Bookstore</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'value':_'recommendation'}</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'value': 'Recommendation'}</t>
+          <t>Recommendation</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'value': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'value':_'book_clubs'}</t>
+          <t>book_clubs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'value': 'Book Clubs'}</t>
+          <t>Book Clubs</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'value':_'excessive_romance'}</t>
+          <t>excessive_romance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'value': 'Excessive Romance'}</t>
+          <t>Excessive Romance</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'value':_'lack_of_romance'}</t>
+          <t>lack_of_romance</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'value': 'Lack of Romance'}</t>
+          <t>Lack of Romance</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'value':_'excessive_description'}</t>
+          <t>excessive_description</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'value': 'Excessive Description'}</t>
+          <t>Excessive Description</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'value':_'not_enough_description'}</t>
+          <t>not_enough_description</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'value': 'Not Enough Description'}</t>
+          <t>Not Enough Description</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'value':_'romance'}</t>
+          <t>romance</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'value': 'Romance'}</t>
+          <t>Romance</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'value':_'fantasy'}</t>
+          <t>fantasy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'value': 'Fantasy'}</t>
+          <t>Fantasy</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'value':_'science_fiction'}</t>
+          <t>science_fiction</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'value': 'Science Fiction'}</t>
+          <t>Science Fiction</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'value':_'horror'}</t>
+          <t>horror</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'value': 'Horror'}</t>
+          <t>Horror</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'value':_'comedy'}</t>
+          <t>comedy</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'value': 'Comedy'}</t>
+          <t>Comedy</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'value':_'mystery'}</t>
+          <t>mystery</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'value': 'Mystery'}</t>
+          <t>Mystery</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'value':_'adventure'}</t>
+          <t>adventure</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'value': 'Adventure'}</t>
+          <t>Adventure</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'value':_'relaxing'}</t>
+          <t>relaxing</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'value': 'Relaxing'}</t>
+          <t>Relaxing</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{'value':_'exciting'}</t>
+          <t>exciting</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'value': 'Exciting'}</t>
+          <t>Exciting</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{'value':_'adventurous'}</t>
+          <t>adventurous</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'value': 'Adventurous'}</t>
+          <t>Adventurous</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'value':_'emotional'}</t>
+          <t>emotional</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'value': 'Emotional'}</t>
+          <t>Emotional</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'value':_'informative'}</t>
+          <t>informative</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'value': 'Informative'}</t>
+          <t>Informative</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'value':_'escape'}</t>
+          <t>escape</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'value': 'Escape'}</t>
+          <t>Escape</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'value':_'learn'}</t>
+          <t>learn</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'value': 'Learn'}</t>
+          <t>Learn</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'value':_'relax'}</t>
+          <t>relax</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'value': 'Relax'}</t>
+          <t>Relax</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'value':_'socialize'}</t>
+          <t>socialize</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'value': 'Socialize'}</t>
+          <t>Socialize</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'value':_'challenge'}</t>
+          <t>challenge</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'value': 'Challenge'}</t>
+          <t>Challenge</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
